--- a/docs/Regla de actividad de estados.xlsx
+++ b/docs/Regla de actividad de estados.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TktFlow\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\TICKET_SYW\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9F7287-DBD4-4152-BBBD-009B03C65900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E329F7-C8E8-46A0-A1C4-F651A3240D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0E5FA1C8-4C7F-4439-A674-539BDB1B6A8E}"/>
+    <workbookView xWindow="39690" yWindow="2955" windowWidth="20790" windowHeight="13455" activeTab="1" xr2:uid="{0E5FA1C8-4C7F-4439-A674-539BDB1B6A8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -183,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="105">
   <si>
     <t>NUEVO</t>
   </si>
@@ -697,6 +698,90 @@
       </rPr>
       <t xml:space="preserve"> y al QM</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Herramienta </t>
+  </si>
+  <si>
+    <t>Proceso</t>
+  </si>
+  <si>
+    <t>Skill</t>
+  </si>
+  <si>
+    <t>Finaciero</t>
+  </si>
+  <si>
+    <t>Compras</t>
+  </si>
+  <si>
+    <t>Contabilida</t>
+  </si>
+  <si>
+    <t>Consultor Compras,Consultor  Ventas</t>
+  </si>
+  <si>
+    <t>JDE</t>
+  </si>
+  <si>
+    <t>APEX</t>
+  </si>
+  <si>
+    <t>Integracion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API REST, JAVA, OIC, Orquetacion </t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desarrollador Sabe herramienta  JDE, BI, BSFN, Orquestador, Java y SQL </t>
+  </si>
+  <si>
+    <t>Consultor Sabe una Herramienta (JDE, SQL, BI ) y especializado en Modulos como Finanzas, compras y Mantenimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desarrollador Sabe Herramienta Java, Python, React y APEX Oracle </t>
+  </si>
+  <si>
+    <t>Desarrollador Sabe Herramienta Java, Python, APEX Oracle, OIC  y JDE</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>Luis C</t>
+  </si>
+  <si>
+    <t>Jimenes</t>
+  </si>
+  <si>
+    <t>Infraestructura Sabe DBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerente Proyecto JDE, SCRUM, BSFN </t>
+  </si>
+  <si>
+    <t>Especialista JDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elias </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antorio </t>
+  </si>
+  <si>
+    <t>Consultor ERP y JDE y Especializado en varios Modulos como Finanzas y Compras</t>
+  </si>
+  <si>
+    <t>Cristian</t>
+  </si>
+  <si>
+    <t>Natalia</t>
   </si>
 </sst>
 </file>
@@ -806,7 +891,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -834,11 +919,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -858,9 +940,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -898,7 +980,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1004,7 +1086,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1146,7 +1228,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1155,23 +1237,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E146533-5EC7-4E38-8841-1A516FBEDF67}">
   <dimension ref="B1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.77734375" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="6" width="21.6640625" customWidth="1"/>
-    <col min="7" max="7" width="21.109375" customWidth="1"/>
-    <col min="8" max="8" width="16.21875" customWidth="1"/>
-    <col min="9" max="9" width="17.88671875" customWidth="1"/>
+    <col min="5" max="6" width="21.7109375" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" customWidth="1"/>
     <col min="10" max="10" width="27" customWidth="1"/>
-    <col min="11" max="11" width="21.6640625" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" customWidth="1"/>
-    <col min="13" max="13" width="13.21875" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="6" t="s">
         <v>4</v>
       </c>
@@ -1200,7 +1282,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="2:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" ht="105" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1229,7 +1311,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="144" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="165" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -1258,7 +1340,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" ht="120" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>36</v>
       </c>
@@ -1287,7 +1369,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="2:10" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" ht="240" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
@@ -1316,8 +1398,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="B6" s="11" t="s">
+    <row r="6" spans="2:10" ht="180" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -1345,7 +1427,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" ht="60" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>37</v>
       </c>
@@ -1368,7 +1450,7 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
     </row>
-    <row r="8" spans="2:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" ht="120" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>1</v>
       </c>
@@ -1397,7 +1479,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" ht="120" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>2</v>
       </c>
@@ -1426,7 +1508,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" ht="135" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>3</v>
       </c>
@@ -1455,7 +1537,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="2"/>
@@ -1466,12 +1548,221 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C13" s="1"/>
-      <c r="E13" s="12"/>
+      <c r="E13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B42A9C4-260A-49CD-AE1A-066C94D68C93}">
+  <dimension ref="C4:O38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="19.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="F23" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" t="s">
+        <v>82</v>
+      </c>
+      <c r="I24" t="s">
+        <v>86</v>
+      </c>
+      <c r="J24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" t="s">
+        <v>88</v>
+      </c>
+      <c r="I25" t="s">
+        <v>88</v>
+      </c>
+      <c r="J25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="K23:O23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>